--- a/docs/project-management/expense-log.xlsx
+++ b/docs/project-management/expense-log.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeffkrystek/Jeff/yek_flashcard/docs/project-management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F1C893-1A69-4948-8D49-E7CC6BD1D16D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8522DA2D-69D5-4D49-8371-FDA203897B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3940" yWindow="780" windowWidth="26840" windowHeight="15680" xr2:uid="{C3AF8066-ADD7-B145-B020-3B8D64D47020}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
   <si>
     <t>Date</t>
   </si>
@@ -86,12 +86,6 @@
     <t>Domain</t>
   </si>
   <si>
-    <t>Domain registration</t>
-  </si>
-  <si>
-    <t>1-year registration</t>
-  </si>
-  <si>
     <t>Apple</t>
   </si>
   <si>
@@ -126,6 +120,39 @@
   </si>
   <si>
     <t>Required for Play Store</t>
+  </si>
+  <si>
+    <t>EXP-005</t>
+  </si>
+  <si>
+    <t>Porkbun</t>
+  </si>
+  <si>
+    <t>Domain registration (annual)</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>yeklanguages.com domain registration</t>
+  </si>
+  <si>
+    <t>1-year registration for jeffkrystek.com</t>
+  </si>
+  <si>
+    <t>EXP-006</t>
+  </si>
+  <si>
+    <t>Domain/Website</t>
+  </si>
+  <si>
+    <t>jeffkrystek.com domain and hosting</t>
+  </si>
+  <si>
+    <t>Domain renewal</t>
+  </si>
+  <si>
+    <t>Future Expenses</t>
   </si>
 </sst>
 </file>
@@ -135,7 +162,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -155,6 +182,13 @@
       <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -178,11 +212,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -517,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22AF5CA4-1A5F-5140-8F8C-A15FB882118C}">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="7.5" bestFit="1" customWidth="1"/>
@@ -527,12 +562,12 @@
     <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="32.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -564,114 +599,208 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" s="2">
-        <v>46219</v>
+        <v>46273</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
       </c>
       <c r="G2" s="3">
-        <v>192</v>
-      </c>
-      <c r="H2" s="3"/>
+        <v>10.08</v>
+      </c>
+      <c r="H2" s="3">
+        <v>10.08</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
       <c r="J2" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" s="2">
-        <v>46219</v>
+        <v>46273</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
       </c>
       <c r="G3" s="3">
-        <v>15.98</v>
-      </c>
-      <c r="H3" s="3"/>
+        <v>121.98</v>
+      </c>
+      <c r="H3" s="3">
+        <v>121.98</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
       <c r="J3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G7" s="3"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G10" s="3">
+        <f>SUM(G2:G8)</f>
+        <v>132.06</v>
+      </c>
+      <c r="H10" s="3">
+        <f>SUM(H2:H8)</f>
+        <v>132.06</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="2">
+        <v>46419</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="3">
+        <v>99</v>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="J14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="2">
+        <v>46419</v>
+      </c>
+      <c r="C15" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" t="s">
+      <c r="D15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" t="s">
         <v>17</v>
       </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="F15" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="3">
-        <v>99</v>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="J4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="G15" s="3">
         <v>25</v>
       </c>
-      <c r="C5" t="s">
+      <c r="J15" t="s">
         <v>26</v>
       </c>
-      <c r="D5" t="s">
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>27</v>
       </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="B16" s="2">
+        <v>46638</v>
+      </c>
+      <c r="C16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="3">
-        <v>25</v>
-      </c>
-      <c r="J5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="G8" s="3">
-        <f>SUM(G2:G6)</f>
-        <v>331.98</v>
-      </c>
-      <c r="H8" s="3">
-        <f>SUM(H2:H6)</f>
-        <v>0</v>
+      <c r="G16" s="3">
+        <v>255</v>
+      </c>
+      <c r="H16" s="3"/>
+      <c r="J16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="2">
+        <v>46623</v>
+      </c>
+      <c r="C17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="3">
+        <v>21.2</v>
+      </c>
+      <c r="H17" s="3"/>
+      <c r="J17" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
